--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/25gps/4mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/25gps/4mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.63179210648</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>629.204200965219</v>
       </c>
-      <c r="W2" t="b">
-        <v>0</v>
+      <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>29</v>
       </c>
       <c r="X2">
-        <v>631.209641866271</v>
+        <v>0.251487798</v>
+      </c>
+      <c r="Y2">
+        <v>0.262821046</v>
+      </c>
+      <c r="Z2">
+        <v>0.3637595562503106</v>
+      </c>
+      <c r="AA2">
+        <v>5.666623999999999</v>
+      </c>
+      <c r="AB2">
+        <v>0.06496757419746084</v>
+      </c>
+      <c r="AC2">
+        <v>40.87787061156192</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.63190842592</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>630.3927001945162</v>
       </c>
-      <c r="W3" t="b">
-        <v>0</v>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>630.8765228047959</v>
+      </c>
+      <c r="X3">
+        <v>0.251454108</v>
+      </c>
+      <c r="Y3">
+        <v>0.262806402</v>
+      </c>
+      <c r="Z3">
+        <v>0.3637256842213116</v>
+      </c>
+      <c r="AA3">
+        <v>5.676147</v>
+      </c>
+      <c r="AB3">
+        <v>0.06485526507235481</v>
+      </c>
+      <c r="AC3">
+        <v>40.88428567079285</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.63202416667</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>631.7940880966289</v>
       </c>
-      <c r="V4">
-        <v>1.296401032581475</v>
-      </c>
-      <c r="W4" t="b">
+      <c r="V4" t="b">
         <v>1</v>
       </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.251431544</v>
+      </c>
+      <c r="Y4">
+        <v>0.262793986</v>
+      </c>
+      <c r="Z4">
+        <v>0.3637011140978154</v>
+      </c>
+      <c r="AA4">
+        <v>5.681221000000001</v>
+      </c>
+      <c r="AB4">
+        <v>0.06479444638780939</v>
+      </c>
+      <c r="AC4">
+        <v>40.93674816931194</v>
+      </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.63213990741</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>631.3703739643975</v>
       </c>
-      <c r="V5">
-        <v>0.7187103865435338</v>
-      </c>
-      <c r="W5" t="b">
+      <c r="V5" t="b">
         <v>1</v>
       </c>
+      <c r="W5">
+        <v>40.86390827647702</v>
+      </c>
+      <c r="X5">
+        <v>0.25141311</v>
+      </c>
+      <c r="Y5">
+        <v>0.26278157</v>
+      </c>
+      <c r="Z5">
+        <v>0.3636793992124616</v>
+      </c>
+      <c r="AA5">
+        <v>5.684229999999999</v>
+      </c>
+      <c r="AB5">
+        <v>0.06475718966192934</v>
+      </c>
+      <c r="AC5">
+        <v>40.88577105373574</v>
+      </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.63225564815</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>629.6225364343647</v>
       </c>
-      <c r="V6">
-        <v>1.151094140309184</v>
-      </c>
-      <c r="W6" t="b">
+      <c r="V6" t="b">
         <v>1</v>
       </c>
+      <c r="X6">
+        <v>0.251405164</v>
+      </c>
+      <c r="Y6">
+        <v>0.262763424</v>
+      </c>
+      <c r="Z6">
+        <v>0.3636607945298347</v>
+      </c>
+      <c r="AA6">
+        <v>5.679130000000001</v>
+      </c>
+      <c r="AB6">
+        <v>0.06481072033381562</v>
+      </c>
+      <c r="AC6">
+        <v>40.80629012471525</v>
+      </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.63237196759</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>629.982908090216</v>
       </c>
-      <c r="V7">
-        <v>0.9228457178521431</v>
-      </c>
-      <c r="W7" t="b">
+      <c r="V7" t="b">
         <v>1</v>
       </c>
+      <c r="X7">
+        <v>0.251391498</v>
+      </c>
+      <c r="Y7">
+        <v>0.262758968</v>
+      </c>
+      <c r="Z7">
+        <v>0.3636481273581771</v>
+      </c>
+      <c r="AA7">
+        <v>5.683734999999999</v>
+      </c>
+      <c r="AB7">
+        <v>0.06475725892484757</v>
+      </c>
+      <c r="AC7">
+        <v>40.79596629742657</v>
+      </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.63248770833</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>630.1832481950792</v>
       </c>
-      <c r="V8">
-        <v>0.28413657706537</v>
-      </c>
-      <c r="W8" t="b">
+      <c r="V8" t="b">
         <v>1</v>
       </c>
+      <c r="X8">
+        <v>0.251380376</v>
+      </c>
+      <c r="Y8">
+        <v>0.262753238</v>
+      </c>
+      <c r="Z8">
+        <v>0.3636362984045817</v>
+      </c>
+      <c r="AA8">
+        <v>5.686430999999999</v>
+      </c>
+      <c r="AB8">
+        <v>0.06472523386498678</v>
+      </c>
+      <c r="AC8">
+        <v>40.78875811722351</v>
+      </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.63260402778</v>
       </c>
@@ -1056,14 +1212,29 @@
       <c r="U9">
         <v>631.3298861852074</v>
       </c>
-      <c r="V9">
-        <v>0.7267811255125107</v>
-      </c>
-      <c r="W9" t="b">
+      <c r="V9" t="b">
         <v>1</v>
       </c>
+      <c r="X9">
+        <v>0.251366074</v>
+      </c>
+      <c r="Y9">
+        <v>0.262745596</v>
+      </c>
+      <c r="Z9">
+        <v>0.3636208896303521</v>
+      </c>
+      <c r="AA9">
+        <v>5.689761000000004</v>
+      </c>
+      <c r="AB9">
+        <v>0.06468558153645988</v>
+      </c>
+      <c r="AC9">
+        <v>40.83794082923718</v>
+      </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>46068.63271976852</v>
       </c>
@@ -1127,14 +1298,29 @@
       <c r="U10">
         <v>632.8786958102351</v>
       </c>
-      <c r="V10">
-        <v>1.352715034109386</v>
-      </c>
-      <c r="W10" t="b">
+      <c r="V10" t="b">
         <v>1</v>
       </c>
+      <c r="X10">
+        <v>0.25136226</v>
+      </c>
+      <c r="Y10">
+        <v>0.26274496</v>
+      </c>
+      <c r="Z10">
+        <v>0.3636177935108638</v>
+      </c>
+      <c r="AA10">
+        <v>5.69135</v>
+      </c>
+      <c r="AB10">
+        <v>0.06466741582291897</v>
+      </c>
+      <c r="AC10">
+        <v>40.92662978742712</v>
+      </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>46068.63283550926</v>
       </c>
@@ -1198,14 +1384,29 @@
       <c r="U11">
         <v>632.7339740726153</v>
       </c>
-      <c r="V11">
-        <v>0.8554938565418075</v>
-      </c>
-      <c r="W11" t="b">
+      <c r="V11" t="b">
         <v>1</v>
       </c>
+      <c r="X11">
+        <v>0.251367344</v>
+      </c>
+      <c r="Y11">
+        <v>0.262732544</v>
+      </c>
+      <c r="Z11">
+        <v>0.3636123365705931</v>
+      </c>
+      <c r="AA11">
+        <v>5.682600000000001</v>
+      </c>
+      <c r="AB11">
+        <v>0.06476366186747938</v>
+      </c>
+      <c r="AC11">
+        <v>40.97816914890532</v>
+      </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>46068.6329518287</v>
       </c>
@@ -1269,11 +1470,26 @@
       <c r="U12">
         <v>630.1491388442727</v>
       </c>
-      <c r="V12">
-        <v>1.535838466411485</v>
-      </c>
-      <c r="W12" t="b">
+      <c r="V12" t="b">
         <v>1</v>
+      </c>
+      <c r="X12">
+        <v>0.251352408</v>
+      </c>
+      <c r="Y12">
+        <v>0.262724586</v>
+      </c>
+      <c r="Z12">
+        <v>0.363596261114261</v>
+      </c>
+      <c r="AA12">
+        <v>5.686089000000003</v>
+      </c>
+      <c r="AB12">
+        <v>0.06472207723033777</v>
+      </c>
+      <c r="AC12">
+        <v>40.78456123090985</v>
       </c>
     </row>
   </sheetData>
